--- a/data/Lead_information_Formulario_Colombia_Main.xlsx
+++ b/data/Lead_information_Formulario_Colombia_Main.xlsx
@@ -481,38 +481,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.co/vans/van-n400-pasajeros</t>
+          <t>https://www.chevrolet.com.co/camionetas/suburban</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/colombia/gm_forms/movs-visid-quote?model=n400</t>
+          <t>https://secure-developments.com/commonwealth/colombia/gm_forms/movs-visid-quote?model=suburban</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Paola Cecilia</t>
+          <t>Catalina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Soto Castillo</t>
+          <t>Reyes Suarez</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>55193099</t>
+          <t>19483340</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3206146522</t>
+          <t>3766185834</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>paolaceciliasotocastillo_co28@mrm.com</t>
+          <t>catalinareyessuarez.co49@mrm.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -523,38 +523,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.co/camionetas/captiva-camionetas-familiares</t>
+          <t>https://www.chevrolet.com.co/vehiculos-electricos/blazer-ev</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/colombia/gm_forms/movs-visid-quote?model=captiva%20xl</t>
+          <t>https://secure-developments.com/commonwealth/colombia/gm_forms/blazer-ev?model=blazer%20ev</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cristian Martín</t>
+          <t>Daniela Camila</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanchez</t>
+          <t>Ibáñez Silva</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70933464</t>
+          <t>82728858</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3402565610</t>
+          <t>3483752380</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cristianmartinsanchez_co02@mrm.com</t>
+          <t>danielacamilaibanezsilva.co89@mrm.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -565,38 +565,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.co/cotizar-bateria</t>
+          <t>https://www.chevrolet.com.co/pickups/colorado-4x4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/colombia/gm_forms/cotizar-bateria?model=posventa</t>
+          <t>https://secure-developments.com/commonwealth/colombia/gm_forms/movs-visid-quote?model=colorado</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lucía Matías</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Flores</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40534451</t>
+          <t>39673392</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3143994126</t>
+          <t>3258282577</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>luciamatiaspinto.co18@mrm.com</t>
+          <t>valentinaflores_co93@mrm.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -618,27 +618,27 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sebastián Rafael</t>
+          <t>Agustina Ignacio</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Castillo</t>
+          <t>Muñoz</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>79688105</t>
+          <t>67329704</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3664065357</t>
+          <t>3621091243</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>sebastianrafaelcastillo_co15@mrm.com</t>
+          <t>agustinaignaciomunoz_co13@mrm.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
